--- a/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -663,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>83,47%</t>
         </is>
       </c>
     </row>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,47; 70,16</t>
+          <t>54,72; 69,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,67; 73,72</t>
+          <t>59,69; 73,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,15; 74,97</t>
+          <t>61,07; 75,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,26; 49,16</t>
+          <t>61,37; 93,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,53; 69,52</t>
+          <t>55,5; 70,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,02; 68,92</t>
+          <t>55,15; 68,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,95; 72,67</t>
+          <t>57,51; 71,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,38; 65,58</t>
+          <t>70,99; 95,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,66; 67,61</t>
+          <t>57,0; 67,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,9; 68,65</t>
+          <t>59,19; 69,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,81; 71,67</t>
+          <t>61,74; 71,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 52,14</t>
+          <t>72,25; 91,9</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>74,58%</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,14; 72,63</t>
+          <t>61,26; 73,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,03; 74,61</t>
+          <t>64,19; 74,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,99; 71,66</t>
+          <t>61,88; 71,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 39,41</t>
+          <t>62,68; 88,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,53; 70,13</t>
+          <t>58,51; 70,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,67; 77,09</t>
+          <t>67,09; 77,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,25; 74,34</t>
+          <t>63,27; 73,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,22; 31,47</t>
+          <t>61,37; 82,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,12; 70,15</t>
+          <t>61,98; 69,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,14; 74,49</t>
+          <t>67,01; 74,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,15; 71,24</t>
+          <t>63,88; 71,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 31,39</t>
+          <t>66,49; 82,75</t>
         </is>
       </c>
     </row>
@@ -943,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,53; 69,75</t>
+          <t>56,86; 70,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,81; 72,44</t>
+          <t>59,85; 72,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,49; 70,88</t>
+          <t>59,16; 70,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,15; 73,43</t>
+          <t>59,13; 87,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,97; 70,45</t>
+          <t>58,26; 70,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,88; 73,03</t>
+          <t>61,39; 73,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,46; 67,42</t>
+          <t>54,86; 67,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 64,32</t>
+          <t>73,94; 94,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,88; 68,41</t>
+          <t>59,79; 68,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,0; 71,09</t>
+          <t>62,62; 71,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,37; 67,65</t>
+          <t>59,17; 67,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,26; 63,39</t>
+          <t>71,33; 88,76</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>77,53%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,3; 64,03</t>
+          <t>52,35; 64,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,67; 65,1</t>
+          <t>53,41; 64,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,1; 66,63</t>
+          <t>55,14; 66,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,09; 55,25</t>
+          <t>61,99; 88,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,53; 70,74</t>
+          <t>58,84; 70,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,21; 66,41</t>
+          <t>54,74; 66,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,42; 69,25</t>
+          <t>57,18; 69,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 44,34</t>
+          <t>65,05; 89,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,93; 65,39</t>
+          <t>57,3; 65,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,19; 64,42</t>
+          <t>55,74; 64,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,82; 65,93</t>
+          <t>57,78; 66,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,25; 43,14</t>
+          <t>66,81; 85,35</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,51; 65,82</t>
+          <t>59,6; 66,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,23; 68,19</t>
+          <t>61,9; 68,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,1; 68,02</t>
+          <t>62,04; 68,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 45,82</t>
+          <t>69,78; 83,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,16; 67,32</t>
+          <t>60,91; 67,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,79</t>
+          <t>62,89; 68,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,87; 67,93</t>
+          <t>61,77; 67,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,06; 39,72</t>
+          <t>73,5; 84,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,38; 65,82</t>
+          <t>61,45; 65,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,63</t>
+          <t>63,41; 67,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,88; 67,16</t>
+          <t>62,75; 67,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,45; 40,44</t>
+          <t>73,63; 82,62</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>72330</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>87582</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>85224</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13769</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81011</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89677</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87351</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>18549</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>153341</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>177259</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>172576</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>32318</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>63230; 80315</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78060; 95904</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76181; 94056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10466; 15871</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>71594; 90411</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>79803; 99551</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>76982; 96081</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>15380; 20757</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>139380; 165225</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>163059; 191015</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>159654; 185525</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>27975; 35586</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>111828</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133440</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>129615</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22533</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>116647</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>150422</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>144106</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36171</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>228474</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>283862</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>273721</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>58704</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>101288; 121605</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123715; 142899</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>119634; 138995</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18162; 25664</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>105269; 126641</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>139893; 160784</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>132861; 154406</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>30524; 40936</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>214002; 241563</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>268871; 297945</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>257640; 287665</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>52336; 65134</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>79524</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89039</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19580</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86280</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>105682</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87715</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>27476</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>165803</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>199935</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>176755</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>47057</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>70829; 87632</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>85026; 102292</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80799; 96894</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15513; 22984</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>77953; 94552</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>96248; 115254</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>78487; 97195</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23423; 29863</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>154482; 177446</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>187150; 213089</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>165482; 189788</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>41312; 51407</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>111906</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>120403</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>117278</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21451</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>117665</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>123060</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>116819</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22397</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>229570</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>243463</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>234097</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>43848</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>100789; 123279</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>108124; 130958</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106224; 127743</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17387; 24695</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>106679; 127393</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>110712; 134784</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>105761; 128311</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>18547; 25616</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>214222; 245686</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>225590; 260762</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>218191; 249511</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>37786; 48274</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1297</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>375587</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>435678</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>421157</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>77333</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>104593</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>777188</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>904518</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>857149</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>181926</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>356422; 394946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>413497; 454263</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>401597; 440376</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>69996; 84020</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>380118; 422228</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>447890; 490760</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>415013; 455541</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>96721; 111564</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>750925; 804747</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>875216; 931656</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>827832; 884042</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>170762; 191593</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,72; 69,51</t>
+          <t>54,48; 69,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,69; 73,34</t>
+          <t>60,26; 74,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,07; 75,4</t>
+          <t>61,14; 74,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61,37; 93,07</t>
+          <t>60,63; 92,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,5; 70,09</t>
+          <t>55,79; 69,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,15; 68,8</t>
+          <t>54,72; 68,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,51; 71,78</t>
+          <t>57,56; 72,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70,99; 95,8</t>
+          <t>70,33; 95,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,0; 67,57</t>
+          <t>57,14; 67,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,19; 69,34</t>
+          <t>59,76; 69,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,74; 71,74</t>
+          <t>61,65; 70,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,25; 91,9</t>
+          <t>71,61; 91,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,26; 73,54</t>
+          <t>61,53; 72,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64,19; 74,14</t>
+          <t>63,51; 74,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,88; 71,9</t>
+          <t>61,59; 72,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,68; 88,57</t>
+          <t>62,28; 88,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,51; 70,39</t>
+          <t>58,84; 70,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,09; 77,11</t>
+          <t>66,8; 76,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,27; 73,52</t>
+          <t>63,04; 73,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>61,37; 82,31</t>
+          <t>60,62; 82,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61,98; 69,96</t>
+          <t>62,04; 70,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,01; 74,26</t>
+          <t>67,08; 74,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63,88; 71,32</t>
+          <t>64,34; 71,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,49; 82,75</t>
+          <t>66,51; 81,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,86; 70,34</t>
+          <t>56,77; 70,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,85; 72,0</t>
+          <t>59,78; 72,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59,16; 70,95</t>
+          <t>58,56; 71,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,13; 87,61</t>
+          <t>57,0; 86,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,26; 70,67</t>
+          <t>58,04; 70,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,39; 73,51</t>
+          <t>61,45; 73,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,86; 67,93</t>
+          <t>54,51; 67,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,94; 94,27</t>
+          <t>73,38; 94,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,79; 68,68</t>
+          <t>59,27; 68,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,62; 71,3</t>
+          <t>62,64; 71,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,17; 67,87</t>
+          <t>59,09; 68,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,33; 88,76</t>
+          <t>70,13; 88,98</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,35; 64,03</t>
+          <t>51,76; 63,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,41; 64,69</t>
+          <t>53,2; 65,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,14; 66,31</t>
+          <t>54,3; 66,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,99; 88,04</t>
+          <t>60,83; 87,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,84; 70,26</t>
+          <t>59,09; 70,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,74; 66,65</t>
+          <t>54,68; 66,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,18; 69,37</t>
+          <t>57,49; 69,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,05; 89,85</t>
+          <t>64,15; 89,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,3; 65,72</t>
+          <t>56,96; 65,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,74; 64,44</t>
+          <t>55,94; 64,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,78; 66,08</t>
+          <t>57,98; 66,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,81; 85,35</t>
+          <t>66,46; 84,69</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,6; 66,04</t>
+          <t>59,76; 66,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61,9; 68,0</t>
+          <t>62,21; 67,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,04; 68,04</t>
+          <t>62,12; 68,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 83,76</t>
+          <t>69,12; 83,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>60,91; 67,66</t>
+          <t>61,26; 67,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,89; 68,9</t>
+          <t>62,72; 68,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,77; 67,8</t>
+          <t>61,91; 67,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,5; 84,78</t>
+          <t>73,8; 85,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,45; 65,85</t>
+          <t>61,26; 65,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,41; 67,5</t>
+          <t>63,39; 67,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,75; 67,01</t>
+          <t>62,82; 67,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,63; 82,62</t>
+          <t>73,72; 83,08</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63230; 80315</t>
+          <t>62949; 80023</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78060; 95904</t>
+          <t>78802; 96943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76181; 94056</t>
+          <t>76264; 93490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10466; 15871</t>
+          <t>10340; 15817</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71594; 90411</t>
+          <t>71967; 90030</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79803; 99551</t>
+          <t>79181; 99144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76982; 96081</t>
+          <t>77047; 96384</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15380; 20757</t>
+          <t>15238; 20613</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139380; 165225</t>
+          <t>139724; 165419</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>163059; 191015</t>
+          <t>164620; 190715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159654; 185525</t>
+          <t>159420; 183493</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27975; 35586</t>
+          <t>27728; 35475</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101288; 121605</t>
+          <t>101746; 120633</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123715; 142899</t>
+          <t>122405; 142892</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119634; 138995</t>
+          <t>119057; 139650</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18162; 25664</t>
+          <t>18045; 25751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>105269; 126641</t>
+          <t>105865; 126276</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>139893; 160784</t>
+          <t>139272; 160120</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132861; 154406</t>
+          <t>132386; 154057</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30524; 40936</t>
+          <t>30151; 41191</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>214002; 241563</t>
+          <t>214200; 241693</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>268871; 297945</t>
+          <t>269153; 297967</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257640; 287665</t>
+          <t>259488; 288654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52336; 65134</t>
+          <t>52353; 64466</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70829; 87632</t>
+          <t>70725; 87595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85026; 102292</t>
+          <t>84931; 102602</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80799; 96894</t>
+          <t>79980; 97679</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15513; 22984</t>
+          <t>14954; 22814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77953; 94552</t>
+          <t>77660; 94555</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96248; 115254</t>
+          <t>96347; 114774</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78487; 97195</t>
+          <t>77988; 97227</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23423; 29863</t>
+          <t>23247; 29925</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154482; 177446</t>
+          <t>153142; 177134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187150; 213089</t>
+          <t>187210; 212772</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165482; 189788</t>
+          <t>165251; 190240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41312; 51407</t>
+          <t>40617; 51537</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100789; 123279</t>
+          <t>99660; 122699</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108124; 130958</t>
+          <t>107694; 131665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106224; 127743</t>
+          <t>104603; 128288</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17387; 24695</t>
+          <t>17062; 24657</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106679; 127393</t>
+          <t>107131; 128493</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>110712; 134784</t>
+          <t>110586; 134672</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105761; 128311</t>
+          <t>106327; 127675</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18547; 25616</t>
+          <t>18289; 25636</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>214222; 245686</t>
+          <t>212959; 245545</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>225590; 260762</t>
+          <t>226378; 260036</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218191; 249511</t>
+          <t>218930; 250090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37786; 48274</t>
+          <t>37587; 47898</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>356422; 394946</t>
+          <t>357395; 395617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>413497; 454263</t>
+          <t>415593; 454096</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>401597; 440376</t>
+          <t>402102; 441011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69996; 84020</t>
+          <t>69339; 83614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>380118; 422228</t>
+          <t>382268; 419985</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>447890; 490760</t>
+          <t>446708; 490247</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415013; 455541</t>
+          <t>415971; 454660</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>96721; 111564</t>
+          <t>97109; 111974</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750925; 804747</t>
+          <t>748592; 803506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>875216; 931656</t>
+          <t>874944; 933318</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>827832; 884042</t>
+          <t>828723; 884751</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>170762; 191593</t>
+          <t>170971; 192659</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18A03-Habitat-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61,97%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>65,26%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>62,6%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>66,97%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>68,32%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>80,74%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,26%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,48; 69,26</t>
+          <t>55,53; 69,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,26; 74,13</t>
+          <t>55,02; 68,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,14; 74,95</t>
+          <t>57,95; 72,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,63; 92,75</t>
+          <t>68,78; 95,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,79; 69,79</t>
+          <t>55,47; 70,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,72; 68,52</t>
+          <t>59,67; 73,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,56; 72,01</t>
+          <t>61,15; 74,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>70,33; 95,14</t>
+          <t>62,69; 93,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57,14; 67,64</t>
+          <t>57,66; 67,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,76; 69,23</t>
+          <t>58,9; 68,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,65; 70,96</t>
+          <t>61,81; 71,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,61; 91,62</t>
+          <t>72,49; 91,66</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>72,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68,62%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>71,98%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>67,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>69,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>67,05%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>77,77%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>72,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>68,62%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,53; 72,96</t>
+          <t>58,53; 70,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,51; 74,14</t>
+          <t>66,67; 77,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61,59; 72,24</t>
+          <t>63,25; 74,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,28; 88,87</t>
+          <t>59,37; 81,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,84; 70,19</t>
+          <t>61,14; 72,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,8; 76,79</t>
+          <t>64,03; 74,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,04; 73,36</t>
+          <t>60,99; 71,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,62; 82,82</t>
+          <t>57,13; 86,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,04; 70,0</t>
+          <t>62,12; 70,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,08; 74,26</t>
+          <t>67,14; 74,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,34; 71,57</t>
+          <t>64,15; 71,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,51; 81,9</t>
+          <t>64,38; 80,93</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>64,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86,89%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>63,83%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>66,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>65,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,3%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,77; 70,31</t>
+          <t>57,97; 70,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,78; 72,22</t>
+          <t>60,88; 73,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,56; 71,52</t>
+          <t>54,46; 67,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,0; 86,96</t>
+          <t>72,84; 95,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,04; 70,67</t>
+          <t>56,53; 69,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,45; 73,2</t>
+          <t>59,81; 72,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,51; 67,95</t>
+          <t>58,49; 70,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>73,38; 94,46</t>
+          <t>54,13; 84,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59,27; 68,56</t>
+          <t>58,88; 68,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62,64; 71,2</t>
+          <t>62,0; 71,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59,09; 68,03</t>
+          <t>58,37; 67,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>70,13; 88,98</t>
+          <t>67,91; 88,31</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78,1%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>58,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>59,47%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>60,88%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>76,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>63,16%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,76; 63,73</t>
+          <t>59,53; 70,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,2; 65,04</t>
+          <t>55,21; 66,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,3; 66,59</t>
+          <t>57,42; 69,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,83; 87,91</t>
+          <t>62,63; 89,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,09; 70,87</t>
+          <t>52,3; 64,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,68; 66,59</t>
+          <t>53,67; 65,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,49; 69,03</t>
+          <t>55,1; 66,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>64,15; 89,92</t>
+          <t>61,08; 88,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,96; 65,68</t>
+          <t>56,93; 65,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55,94; 64,26</t>
+          <t>56,19; 64,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,98; 66,23</t>
+          <t>57,82; 65,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,46; 84,69</t>
+          <t>66,45; 85,3</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>65,83%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79,23%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>62,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>65,22%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>65,07%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,09%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>65,83%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,76; 66,15</t>
+          <t>61,16; 67,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,21; 67,98</t>
+          <t>62,72; 68,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,12; 68,13</t>
+          <t>61,87; 67,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,12; 83,35</t>
+          <t>72,99; 84,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,26; 67,3</t>
+          <t>59,51; 65,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,72; 68,83</t>
+          <t>62,23; 68,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,91; 67,67</t>
+          <t>62,1; 68,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>73,8; 85,09</t>
+          <t>67,41; 82,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61,26; 65,75</t>
+          <t>61,38; 65,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,39; 67,62</t>
+          <t>63,41; 67,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,82; 67,07</t>
+          <t>62,88; 67,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,72; 83,08</t>
+          <t>72,72; 82,04</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81011</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89677</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>87351</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17158</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>72330</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>87582</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>85224</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13769</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81011</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89677</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87351</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32318</t>
+          <t>31209</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62949; 80023</t>
+          <t>71629; 89675</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78802; 96943</t>
+          <t>79609; 99723</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76264; 93490</t>
+          <t>77565; 97273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10340; 15817</t>
+          <t>13786; 19074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71967; 90030</t>
+          <t>64095; 81072</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79181; 99144</t>
+          <t>78027; 96402</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77047; 96384</t>
+          <t>76278; 93514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15238; 20613</t>
+          <t>10747; 15969</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139724; 165419</t>
+          <t>141002; 165347</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164620; 190715</t>
+          <t>162243; 189119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159420; 183493</t>
+          <t>159822; 185328</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27728; 35475</t>
+          <t>26957; 34085</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>206</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>150422</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144106</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32673</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>111828</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>133440</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>129615</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22533</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>116647</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>150422</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>144106</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58704</t>
+          <t>52938</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101746; 120633</t>
+          <t>105305; 126181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>122405; 142892</t>
+          <t>139005; 160728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119057; 139650</t>
+          <t>132822; 156124</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18045; 25751</t>
+          <t>26949; 36989</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>105865; 126276</t>
+          <t>101096; 120095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>139272; 160120</t>
+          <t>123412; 143798</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132386; 154057</t>
+          <t>117899; 138540</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30151; 41191</t>
+          <t>15395; 23389</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>214200; 241693</t>
+          <t>214477; 242201</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>269153; 297967</t>
+          <t>269409; 298888</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>259488; 288654</t>
+          <t>258719; 287325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52353; 64466</t>
+          <t>46573; 58548</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86280</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>105682</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>87715</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26226</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>79524</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>94253</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>89039</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19580</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>86280</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>105682</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87715</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47057</t>
+          <t>42996</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70725; 87595</t>
+          <t>77564; 94259</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84931; 102602</t>
+          <t>95450; 114497</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79980; 97679</t>
+          <t>77916; 96470</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14954; 22814</t>
+          <t>21984; 28703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77660; 94555</t>
+          <t>70418; 86887</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>96347; 114774</t>
+          <t>84974; 102915</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77988; 97227</t>
+          <t>79874; 96806</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23247; 29925</t>
+          <t>12839; 19987</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>153142; 177134</t>
+          <t>152119; 176746</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187210; 212772</t>
+          <t>185281; 212442</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165251; 190240</t>
+          <t>163225; 189191</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40617; 51537</t>
+          <t>36603; 47600</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>117665</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123060</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116819</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>20386</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>111906</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>120403</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>117278</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21451</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>117665</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>123060</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>116819</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43848</t>
+          <t>41462</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99660; 122699</t>
+          <t>107928; 128258</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107694; 131665</t>
+          <t>111649; 134299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104603; 128288</t>
+          <t>106200; 128080</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17062; 24657</t>
+          <t>16348; 23292</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>107131; 128493</t>
+          <t>100709; 123294</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>110586; 134672</t>
+          <t>108657; 131796</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106327; 127675</t>
+          <t>106154; 128357</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18289; 25636</t>
+          <t>16921; 24387</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212959; 245545</t>
+          <t>212850; 244454</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>226378; 260036</t>
+          <t>227379; 260713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218930; 250090</t>
+          <t>218353; 248969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37587; 47898</t>
+          <t>35751; 45897</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>629</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>401602</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>468840</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>435992</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>96443</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>375587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>435678</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>421157</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>77333</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>401602</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>468840</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>435992</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>72162</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>181926</t>
+          <t>168605</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>357395; 395617</t>
+          <t>381638; 420087</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415593; 454096</t>
+          <t>446719; 489949</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>402102; 441011</t>
+          <t>415725; 456400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69339; 83614</t>
+          <t>88848; 103108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>382268; 419985</t>
+          <t>355869; 393637</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446708; 490247</t>
+          <t>415703; 455491</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>415971; 454660</t>
+          <t>401981; 440299</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97109; 111974</t>
+          <t>64389; 78663</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>748592; 803506</t>
+          <t>750086; 804351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>874944; 933318</t>
+          <t>875273; 933404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>828723; 884751</t>
+          <t>829481; 885929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>170971; 192659</t>
+          <t>157965; 178217</t>
         </is>
       </c>
     </row>
